--- a/文档/MEE设计.xlsx
+++ b/文档/MEE设计.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,53 +11,229 @@
     <sheet name="基础物品" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="加载与开关" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="食谱门控框架" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="待补充(后续填)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="负面效果与心情联动" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="待补充(后续填)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="雨水收集系统" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="30">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
-      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -67,26 +242,221 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
+        <fgColor rgb="FF2F5496"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FC"/>
+        <fgColor rgb="FFF2F6FC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -96,47 +466,350 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -489,7 +1162,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -500,28 +1172,28 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metabolic Essential（代谢扩展模块）设计文档</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>仅记录当前已实现的架构与内容；数值/配方等为占位，后续由作者补充。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>模块名称</t>
         </is>
@@ -532,8 +1204,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>对应 DLL</t>
         </is>
@@ -544,8 +1216,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>接口契约</t>
         </is>
@@ -556,8 +1228,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>加载方式</t>
         </is>
@@ -568,8 +1240,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>默认状态</t>
         </is>
@@ -580,8 +1252,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>设计核心</t>
         </is>
@@ -592,20 +1264,20 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>当前实现度</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>需求×4 + 基础物品×4 + 开关框架 + 食谱门控框架 已就位；数值为占位、消费/配方待补</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+          <t>需求×4 + 基础物品×4 + 开关框架 + 食谱门控框架 已就位；消费(自动摄入)已就位，配方已配(酿造台/炉灶/切石机/水井)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="33" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>源码位置</t>
         </is>
@@ -627,97 +1299,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="16.125" customWidth="1" min="4" max="4"/>
+    <col width="7.875" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="10" max="11"/>
+    <col width="24.75" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代谢需求（Need_MEE_*）</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>基类 Need_MEE_Base：MaxLevel=1、初始满值、阈值{0.15,0.3,0.7}；NeedInterval 每150 tick 触发，消耗 = FallPerDay×150/60000。显示/消耗均由开关标志控制。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>需求类名</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>DefName</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>对应物品(DefName)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>FallPerDay
 (每日消耗/占位)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>MaxLevel</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>初始值</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>需求栏显示
 (IsLoadedMME)</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>是否消耗
 (Active)</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>补充API</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-    </row>
-    <row r="5">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>补充(摄入)方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Need_MEE_Water</t>
@@ -764,66 +1440,96 @@
           <t>Satisfy(amount)</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>已实现(数值占位)</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>水井</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>消耗的逻辑，日常正常掉落，当劳损减少的时候也会减少水</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>摄入对应物品自动补充(Comp_MEE_Satisfier.PostIngested→Satisfy，单次回50%)；需求&lt;0.5 时 JobGiver_SatisfyMetabolic 自动摄入对应补剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Need_MEE_Sugar</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>MEESugar</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>糖</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>MEE_RawSugar</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>糖浆</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMash</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>满值</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>模块加载后</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>模块激活后</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Satisfy(amount)</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>已实现(数值占位)</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>植被</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>消耗的逻辑，日常正常掉落，当皮质醇减少的时候也会减少糖，但是会减慢皮质醇的上升</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>摄入对应物品自动补充(Comp_MEE_Satisfier.PostIngested→Satisfy，单次回50%)；需求&lt;0.5 时 JobGiver_SatisfyMetabolic 自动摄入对应补剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Need_MEE_Electrolytes</t>
@@ -870,62 +1576,92 @@
           <t>Satisfy(amount)</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>已实现(数值占位)</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>石头</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>消耗的逻辑，日常掉落，当劳损减少的时候也会少量减少糖</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>摄入对应物品自动补充(Comp_MEE_Satisfier.PostIngested→Satisfy，单次回50%)；需求&lt;0.5 时 JobGiver_SatisfyMetabolic 自动摄入对应补剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Need_MEE_Protein</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>MEEProtein</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>蛋白质</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>MEE_ProteinExtract</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>满值</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>模块加载后</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>模块激活后</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Satisfy(amount)</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>已实现(数值占位)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>吃的</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>当体魄上升的时候，会需要减少蛋白质</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>摄入对应物品自动补充(Comp_MEE_Satisfier.PostIngested→Satisfy，单次回50%)；需求&lt;0.5 时 JobGiver_SatisfyMetabolic 自动摄入对应补剂</t>
         </is>
       </c>
     </row>
@@ -940,88 +1676,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="2" max="6"/>
+    <col width="10" customWidth="1" min="7" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>基础物品（ThingDef，ParentName=ResourceBase）</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>均为 category=Item、resource=true 的基础资源；贴图为原版占位，后续换专用贴图。物品本身常驻（无隐藏机制）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+          <t>均为 category=Item、resource=true 的基础资源；贴图为本地占位 PNG（Textures/Things/Item/MEE/MEE_*.png，由 gen_placeholders.py 生成），后续可换专用贴图。物品本身常驻（无隐藏机制）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>DefName</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>英文label</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>对应需求</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>贴图(占位)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>堆叠上限</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>市场价值</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>质量Mass</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>MEE_WaterBottle</t>
@@ -1029,12 +1759,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>水瓶</t>
+          <t>饮用水</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>water bottle</t>
+          <t>drinking water</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1049,7 +1779,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>MedicineHerbal</t>
+          <t>本地占位PNG(MEE_WaterBottle.png)</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
@@ -1061,59 +1791,59 @@
       <c r="I5" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>已实现(占位图)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>MEE_RawSugar</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>生砂糖</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>raw sugar</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMash</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>葡萄糖糖浆</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>glucose syrup</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Sugar</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>ResourceBase</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>本地占位PNG(MEE_GlucoseMash.png)</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>已实现(占位图)</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>MEE_Salt</t>
@@ -1153,55 +1883,285 @@
       <c r="I7" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>已实现(占位图)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>MEE_ProteinExtract</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>蛋白质提取物</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>protein extract</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Protein</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>ResourceBase</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>已实现(占位图)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MEE_RawWater</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>生水</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>raw water</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ResourceBase</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>本地占位PNG(MEE_RawWater.png)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>已实现(占位图·饮用25%概率致病)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MEE_LightSaltWater</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>淡盐水</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>light salt water</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ResourceBase</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>本地占位PNG(MEE_LightSaltWater.png)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>已实现(占位图)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MEE_FunctionalDrink</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>功能饮品</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>functional drink</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ResourceBase</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>本地占位PNG(MEE_FunctionalDrink.png)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>已实现(占位图)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MEE_VegFruitJuice</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>果蔬汁</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>veg-fruit juice</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ResourceBase</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>本地占位PNG(MEE_VegFruitJuice.png)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>已实现(占位图)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MEE_MilkTea</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>milk tea</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ResourceBase</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>本地占位PNG(MEE_MilkTea.png)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>已实现(占位图·Nutrition=0.33)</t>
         </is>
       </c>
     </row>
@@ -1217,45 +2177,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>加载与开关机制</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>显示 ≠ 激活：IsLoadedMME 控制需求栏是否出现；Active 控制是否真正消耗/生效。两者在 Init 成功后同步置 true。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>标志 / 类</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>作用</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>设置点 / 触发</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="33" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>MetabolicState.Active</t>
@@ -1272,24 +2232,24 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>MetabolicState.IsLoadedMME</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>控制四个需求是否在需求栏显示（ShowOnNeedList）</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>同上，与 Active 同步置 true；TryLoad 开头先置 false</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="33" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>MetabolicLoader</t>
@@ -1306,25 +2266,25 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="33" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>RimHormonesMod.Settings
 .EnableMetabolicEssential</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>游戏内开关（默认 false），ModSettings + Scribe 持久化</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>设置界面复选框</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>重启约束</t>
@@ -1353,45 +2313,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>食谱门控框架（MEE 食谱显隐）</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>RecipeDef 无 ShowOnNeedList，改用 Harmony postfix 拦 AvailableNow。patch 在主 mod 常驻（模块关闭时食谱也必须藏起来）。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>组件</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>类型 / 位置</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>作用</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>MEERecipeMarker</t>
@@ -1408,24 +2368,24 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6" ht="33" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>RecipeDef_AvailableNow_MEE_Patch</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Harmony postfix（主 mod 常驻）</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>原逻辑可用 + 是 MEE 食谱 + IsLoadedMME=false → 翻 AvailableNow=false（菜单隐藏且不可做）</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="33" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>当前 MEE 食谱</t>
@@ -1453,135 +2413,1375 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>负面效果 / 心情 / 联动 设计（已实现 · 2026-08-13）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>数值为代码实际常量；草稿未给处的为暂定值，可在『作者补充』列标注调整。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>一、低代谢需求负面效果（Hediff + 心情）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>效果名</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>数值 / 效果</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>DefName</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>持续 / 解除</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>源文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>脱水</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Hediff</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Water &lt; 25% 持续 12h (30000t)</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>意识 Consciousness -0.10</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>MEE_Dehydration</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>8h(20000t) 后消退，可叠加/刷新</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Hediffs.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>水中毒</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Hediff</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>饮水前 Water &gt; 90% 且 60% 概率</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>意识 -0.20 / 工作效率 -0.20 / 想吐 vomitMtbDays=0.5</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>MEE_WaterPoisoning</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>24h(60000t)，无法医疗</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Hediffs.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>水中毒心情</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Thought</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>触发水中毒时</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>心情 -8</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>MEE_WaterPoisoningMood</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>随 Hediff 24h</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Hediffs.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>浑身无力</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Hediff</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>电解质 &lt; 30%</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>工作效率 WorkSpeed -0.20</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>MEE_Weakness</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>电解质 ≥30% 后解除</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Hediffs.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>浑身无力心情</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Thought</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>电解质 &lt; 30%</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>心情 -6</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>MEE_WeaknessMood</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>恢复后解除</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Hediffs.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>我需要水（重）</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Thought</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Water &lt; 15%</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>心情 -6</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>MEE_NeedWater</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Water ≥15% 后解除</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Hediffs.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>我渴了（轻）</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Thought</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Water &lt; 30%</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>心情 -3</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>MEE_Thirsty</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Water ≥30% 后解除</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Hediffs.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>吃了糖</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Thought</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>摄入葡萄糖原浆 (MEE_GlucoseMash)</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>心情 +1</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>MEE_AteSugar</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>0.3 天</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Hediffs.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>营养不足</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Hediff</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>蛋白质 &lt; 10%（经 PhysiqueUpgradeGate）</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>纯标记 Hediff，无数值惩罚</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>MEE_Malnutrition</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>蛋白 ≥10% 后解除</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>MetabolicLogic_Protein.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>二、蛋白质 ↔ 体魄升级联动（MetabolicLogic_Protein.cs）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>每升 1 级体魄消耗蛋白质</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>15% (0.15)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>ProteinCostPerLevel，按升级跨度等比扣减（跨多级累加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>禁止升级阈值</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>蛋白 &lt; 10% (0.10)</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>MalnutritionThreshold；低于则 PhysiqueUpgradeGate 返回 allow=false（无法获体魄经验/升级）+ 挂营养不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>解除条件</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>蛋白 ≥ 10%</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>恢复后解除门控与营养不足 Hediff</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>三、劳损 → 额外消耗（复用劳损窗口 ≈50s / 3000t，MetabolicLogic_Sugar.cs）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>基础每日消耗</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>劳损窗口额外(+)</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>劳损时合计 / 日</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>水 Water</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>+0.40</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>电解质 Electrolytes</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>+0.33</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>糖 Sugar（已有）</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>+0.20</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>0.60（皮质醇&gt;20% 时再 -0.10 → 0.30）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>注：劳损窗口 StrainActiveWindowTicks=3000(≈50s)，窗口内视为『正在训练/执行劳损』，覆盖连续动作间隔；停止训练后窗过期不再加成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>四、糖 ↔ 皮质醇联动（已有，MetabolicLogic_Sugar.cs）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>皮质醇 &gt; 20% &amp; 糖 &gt; 33%</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>抑制皮质醇增长</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>+10% / 日</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>皮质醇 &gt; 20% &amp; 糖 ≤ 33%</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>催高皮质醇增长</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>-13% / 日（额外增长）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>皮质醇 &gt; 20%</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>糖每日消耗</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>40% → 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>执行劳损窗口内</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>糖额外消耗</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>+20% / 日</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>五、饮品 Buff（功能饮品 / 果蔬汁 / 奶茶 / 淡盐水，12h 限时 Hediff，HediffComp_MEEBuff 经解耦接口施加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>饮品</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Buff DefName</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>核心效果（代码常量）</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>心情</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>持续</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>源文件</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>淡盐水</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MEE_Buff_LightSaltWater</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>劳损恢复效率 ×0.75（恢复 -25%）</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>12h(30000t)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HediffComp_MEEBuff.cs → Need_MuscleStrain.SetExtraStrainRecoveryMultiplier</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>摄入即挂，可叠加刷新</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>功能饮品</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MEE_Buff_FunctionalDrink</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>即时劳损 -25%（摄入 ReduceStrain）+ 视为锻炼(markExercise)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HediffComp_MEEBuff.cs(moodThought→TryGainMemory) + ThoughtDef MEE_Thought_FunctionalDrink（HediffStage 无 baseMoodEffect，心情改走记忆）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>果蔬汁</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MEE_Buff_VegFruitJuice</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>体魄总经验 +25%（PhysiqueXpMultUtility.SetExtraXpMult=1.25）</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>HediffComp_MEEBuff.cs + ThoughtDef MEE_Thought_VegFruitJuice</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>isBad=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MEE_Buff_MilkTea</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>皮质醇额外衰减 -3.25/区间(≈-13%/日) + 摄入供 33% 饱食度(Nutrition=0.33)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>HediffComp_MEEBuff.cs → Need_Cortisol.SetExtraCortisolDecay + ThoughtDef MEE_Thought_MilkTea</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>生水</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>(无 Buff)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>饮用 25% 概率致病 FoodPoisoning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Comp_MEE_Satisfier.sicknessChance</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>烧开(MEE_BoilWater)后变安全饮用水</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>待补充项（以下为当前缺口，供作者后续填写）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>『当前状态』列描述已有基础；『作者补充 / 备注』列留空，由你填写具体设计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>当前状态</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>作者补充 / 备注（留空待填）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>物品专用贴图</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>本地占位PNG（MEE_Salt/ProteinExtract/WaterBottle/GlucoseMash，新增 RawWater/LightSaltWater/FunctionalDrink/VegFruitJuice/MilkTea），由 gen_placeholders.py 生成；后续换专用贴图</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>进食/饮水消费逻辑</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>已实现：Comp_MEE_Satisfier(PostIngested→Satisfy，单次回50%) + JobGiver_SatisfyMetabolic(需求&lt;阈值0.5自动摄入对应补剂)；阈值0.5与单次50%暂定、后续可微调</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>需求→物品映射：水→MEE_WaterBottle、糖→MEE_GlucoseMash、电解质→MEE_Salt、蛋白质→MEE_ProteinExtract</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MEE 制作配方</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>已配：MEE_MakeGlucoseMashFromCorn/Fruit(酿造台·玉米/野果，去土豆)、MEE_MakeProteinExtractFromMilk/Eggs/Meat(炉灶)、MEE_MakeSaltFromStone(切石机)、MEE_MakeWaterBottle(水井/取水机器打生水)、MEE_BoilWater(营火/燃木灶/电灶烧水)、MEE_MakeLightSaltWater/FunctionalDrink/VegFruitJuice/MilkTea(带火建筑调制饮品)；均带 MEERecipeMarker 门控，仅模块启用可见</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>均带 MEERecipeMarker 门控，仅模块启用可见</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>数值平衡</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>FallPerDay 占位(0.6/0.4/0.3/0.15)，阈值{0.15,0.3,0.7}</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>低代谢需求负面效果(Hediff) + 心情</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>已实现：脱水/水中毒/浑身无力/营养不足 + 缺水(重/轻)/吃糖/水中毒心情，详见『负面效果与心情联动』表</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>数值为代码实际常量；糖/水联动阈值可微调</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>需求图标 / 曲线样式</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>默认条状；无定制图标</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>跨 mod 兼容 / 依赖</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>仅依赖主 mod IMetabolicModule；暂未声明前置</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>吃肉补电解质</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>已实现：MEE_MeatElectrolytesPatch(Thing.Ingested postfix)，吃肉(FoodTypeFlags.Meat)时额外补充电解质 0.15，仅模块启用(Active)生效</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>与糖/水联动阈值可微调</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>待补充项（以下为当前缺口，供作者后续填写）</t>
-        </is>
-      </c>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>雨水收集系统（MEE_RainwaterCollector）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>『当前状态』列描述已有基础；『作者补充 / 备注』列留空，由你填写具体设计。</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>被动建筑：下雨/下雪时自动把落水收集成饮用水瓶，无电、无账单、无殖民者操作。</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>作者补充 / 备注（留空待填）</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>物品专用贴图</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>占位原版贴图(Silver/Steel/Gold/MedicineHerbal)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DefName</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MEE_RainwaterCollector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>建筑 defName</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>进食/饮水消费逻辑</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Satisfy(amount) API 已就绪，未接 ingest 调用</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>中文名</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>雨水收集器</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>label（已注入 zh/en）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>MEE 制作配方</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>门控框架就绪，无具体配方；需配 RecipeDef + MEERecipeMarker</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>英文名</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rainwater collector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>数值平衡</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>FallPerDay 占位(0.6/0.4/0.3/0.15)，阈值{0.15,0.3,0.7}</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>占用</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>size=(2,2)，Impassable</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>低代谢需求负面效果(Hediff)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>未实现；需求低时无惩罚</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>被动建筑</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BuildingBase；无 Power/Flickable/Bill 组件</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>需求图标 / 曲线样式</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>默认条状；无定制图标</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>模块门控</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MEEBuildingMarker + MetaBolicLoadCtrl.Active</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>模块关→建造菜单隐藏；Active=false→不产水</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>跨 mod 兼容 / 依赖</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>仅依赖主 mod IMetabolicModule；暂未声明前置</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>weatherManager.RainRate&gt;0 或 SnowRate&gt;0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>下雨或下雪（含 Rain/Snow/RainSnow/SnowHard）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>收集逻辑</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Comp_MEE_RainwaterCollector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>每 tick 按强度累积：bottlesPerDay×intensity/60000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MEE_WaterBottle</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>缓冲满 1 瓶即生成，落到建筑 8 邻格可站立空地</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>收集速率</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bottlesPerDay = 3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>满强度整日降水约 3 瓶（被动免费，慢于水井人工产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>缓冲上限</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>maxStored = 10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>瓶；满了暂停收集，待产出释放后继续</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>造价</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>木 60 + 钢 30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>costList</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>血量 / 建造</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>220 / 2200</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MaxHitPoints / WorkToBuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>贴图</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>占位纯色块（蓝水箱）</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Textures/Things/Building/MEE/MEE_RainwaterCollector.png，后续可换专用</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>已实现（2026-08-16）</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DLL + XML + 贴图 + 语言已部署 Steam 副本</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/文档/MEE设计.xlsx
+++ b/文档/MEE设计.xlsx
@@ -14,6 +14,9 @@
     <sheet name="负面效果与心情联动" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="待补充(后续填)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="雨水收集系统" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="建筑" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="配方" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="问题" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -23,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="30">
+  <fonts count="34">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -232,8 +235,27 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -455,8 +477,18 @@
         <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -577,6 +609,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -725,7 +771,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -757,6 +803,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1293,6 +1351,1044 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>配方（RecipeDef，全部带 MEERecipeMarker 门控，模块关闭时隐藏）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>原料/产物格式：DefName x数量；分类用 (分类)。批量配方为同比例放大。数据取自当前 XML。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>DefName</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>中文名</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>制作台</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>原料</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>产物</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>工时</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>技能要求</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>MEE门控</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>MEE_BoilWater</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>烧水</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Campfire, FueledStove, ElectricStove</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>MEE_RawWaterx1</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>MEE_WaterBottlex1</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>MEE_BoilWaterBulk12</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>烧水(批量12→10)</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Campfire, FueledStove, ElectricStove</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>MEE_RawWaterx12</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>MEE_WaterBottlex10</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>MEE_BoilWaterBulk30</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>烧水(批量30→25)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Campfire, FueledStove, ElectricStove</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>MEE_RawWaterx30</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>MEE_WaterBottlex25</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeFunctionalDrink</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>制作功能饮料</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Campfire, FueledStove, ElectricStove</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>MEE_WaterBottlex1 + MEE_GlucoseMashx1</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>MEE_FunctionalDrinkx2</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeGlucoseMashFromCorn</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>玉米制葡萄糖糖浆</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Brewery</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>RawCornx10</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMashx5</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeGlucoseMashFromCornBulk10</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>玉米制糖浆(批量100→50)</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Brewery</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>RawCornx100</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMashx50</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeGlucoseMashFromCornBulk5</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>玉米制糖浆(批量50→25)</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Brewery</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>RawCornx50</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMashx25</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeGlucoseMashFromFruit</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>水果制葡萄糖糖浆</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Brewery</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>RawBerriesx10</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMashx1</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>产出比玉米低(见问题#1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeGlucoseMashFromFruitBulk10</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>水果制糖浆(批量100→10)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Brewery</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>RawBerriesx100</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMashx10</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>产出比玉米低(见问题#1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeGlucoseMashFromFruitBulk5</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>水果制糖浆(批量50→5)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Brewery</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>RawBerriesx50</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMashx5</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>产出比玉米低(见问题#1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeLightSaltWater</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>制作淡盐水</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Campfire, FueledStove, ElectricStove</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>MEE_WaterBottlex1 + MEE_Saltx1</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>MEE_LightSaltWaterx5</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeMilkTea</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>制作奶茶</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Campfire, FueledStove, ElectricStove</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>MEE_WaterBottlex1 + Milkx1</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MilkTeax2</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeProteinExtractFromMilk</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>牛奶制蛋白质提取物</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>ElectricSmelter</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Milkx10</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>MEE_ProteinExtractx1</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>注释称烹饪台，实际用熔炼炉(见问题#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeProteinExtractFromEggs</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>鸡蛋制蛋白质提取物</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>ElectricSmelter</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>EggChickenUnfertilized,EggChickenFertilizedx10</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>MEE_ProteinExtractx1</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>注释称烹饪台，实际用熔炼炉(见问题#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeProteinExtractFromMeat</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>生肉制蛋白质提取物</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>ElectricSmelter</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>(MeatRaw)x5</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>MEE_ProteinExtractx1</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>Cooking&gt;=2</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>注释称烹饪台，实际用熔炼炉(见问题#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeSaltFromStone</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>石块研磨盐</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>TableStonecutter</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>(StoneChunks)x1</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>MEE_Saltx5</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>Crafting&gt;=2</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MakeVegFruitJuice</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>制作蔬果汁</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Campfire, FueledStove, ElectricStove</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>MEE_WaterBottlex1 + RawBerriesx5</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>MEE_VegFruitJuicex2</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>当前配方/建筑潜在问题（自动比对 XML 得出，待作者确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>updated 2026-08-18 22:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>问题描述</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>平衡</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>MEE_MakeGlucoseMashFromCorn* vs MEE_MakeGlucoseMashFromFruit*</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>葡萄糖糖浆产出严重失衡：玉米 10→5(2:1)，水果 10→1(10:1)。玉米每单位原料/每工时的产出均为水果的 5 倍。</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>统一水果产出比例（如 10→3~5），或确认水果本应显著低效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>MEE_MakeProteinExtractFrom*</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>配方注释写『在烹饪台加工』，但 recipeUsers=ElectricSmelter（熔炼炉），台子语义不符。</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>改为 ElectricStove；或把注释改成熔炼语义。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>命名</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>MEE_MakeGlucoseMashFromCorn (label)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>基础玉米配方 label='make glucose mash (corn)'，其余配方与物品本体 label 均为 'glucose syrup'。</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>统一为 'glucose syrup'。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>过时</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>雨水收集系统 sheet</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>该表仍引用已重命名的 MEE_RainwaterCollector（现拆为 MEE_SimpleRainwaterCollector 与 MEE_MoistureCollector）。</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>以本工作簿『建筑』sheet 为准，旧表可删或合并。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>提示</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>MEE_MilkTea</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>同时为 Fluid + MealAwful + Nutrition 0.33，既是饮品又是餐食。确认是否符合预期。</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>若只作饮品，改 preferability=NeverForNutrition、Nutrition=0。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1676,492 +2772,689 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="6"/>
-    <col width="10" customWidth="1" min="7" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="6"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="9"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>基础物品（ThingDef，ParentName=ResourceBase）</t>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>基础物品（ThingDef，MEE 代谢资源/饮品）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>均为 category=Item、resource=true 的基础资源；贴图为本地占位 PNG（Textures/Things/Item/MEE/MEE_*.png，由 gen_placeholders.py 生成），后续可换专用贴图。物品本身常驻（无隐藏机制）。</t>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>均为 category=Item；Nutrition=0 者为补剂（非饭），由 Comp_MEE_Satisfier 补充对应需求。数据取自当前 XML。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>DefName</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>英文label</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>对应需求</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>贴图(占位)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>堆叠上限</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>市场价值</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>质量Mass</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>堆叠</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>质量</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>营养</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>可食性</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>食物类型</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>补剂效果(需求+比例)</t>
+        </is>
+      </c>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>其它效果</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>MEE_FunctionalDrink</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>功能饮料</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>functional drink</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Foods</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>NeverForNutrition</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>MEEWater +0.5</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>buff:MEE_Buff_FunctionalDrink 劳损:-0.25</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>MEE_GlucoseMash</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>葡萄糖糖浆</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>glucose syrup</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Foods</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>NeverForNutrition</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>MEESugar +0.5</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr"/>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>MEE_LightSaltWater</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>淡盐水</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>light salt water</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Foods</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>NeverForNutrition</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>MEEWater +0.5</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>buff:MEE_Buff_LightSaltWater</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MilkTea</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>milk tea</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Foods</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>MealAwful</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>MEEWater +0.5</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>buff:MEE_Buff_MilkTea</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>MEE_ProteinExtract</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>蛋白质提取物</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>protein extract</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>MEE_Ingredients</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>NeverForNutrition</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>AnimalProduct</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>MEEProtein +0.5</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr"/>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>MEE_RawWater</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>生水</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>raw water</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Foods</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>NeverForNutrition</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>MEEWater +0.5</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>致病率:0.25→FoodPoisoning</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>MEE_Salt</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>盐</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>salt</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>MEE_Ingredients</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>NeverForNutrition</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>MEEElectrolytes +0.5</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr"/>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>MEE_VegFruitJuice</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>蔬果汁</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>veg-fruit juice</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Foods</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>NeverForNutrition</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>MEEWater +0.5</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>buff:MEE_Buff_VegFruitJuice</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>MEE_WaterBottle</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>饮用水</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>drinking water</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>本地占位PNG(MEE_WaterBottle.png)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>已实现(占位图)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>MEE_GlucoseMash</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>葡萄糖糖浆</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>glucose syrup</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Sugar</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>本地占位PNG(MEE_GlucoseMash.png)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>已实现(占位图)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>MEE_Salt</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>盐</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>salt</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Electrolytes</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Steel</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>已实现(占位图)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>MEE_ProteinExtract</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>蛋白质提取物</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>protein extract</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Protein</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>已实现(占位图)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MEE_RawWater</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>生水</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>raw water</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>本地占位PNG(MEE_RawWater.png)</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>50</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>已实现(占位图·饮用25%概率致病)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MEE_LightSaltWater</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>淡盐水</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>light salt water</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>本地占位PNG(MEE_LightSaltWater.png)</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>50</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>已实现(占位图)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MEE_FunctionalDrink</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>功能饮品</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>functional drink</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>本地占位PNG(MEE_FunctionalDrink.png)</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>50</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>已实现(占位图)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MEE_VegFruitJuice</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>果蔬汁</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>veg-fruit juice</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>本地占位PNG(MEE_VegFruitJuice.png)</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>50</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>已实现(占位图)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MEE_MilkTea</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>奶茶</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>milk tea</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ResourceBase</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>本地占位PNG(MEE_MilkTea.png)</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>50</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>已实现(占位图·Nutrition=0.33)</t>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Foods</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>NeverForNutrition</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>MEEWater +0.5</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr"/>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>已实现</t>
         </is>
       </c>
     </row>
@@ -3485,7 +4778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3494,8 +4787,6 @@
           <t>雨水收集系统（MEE_RainwaterCollector）</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3503,14 +4794,8 @@
           <t>被动建筑：下雨/下雪时自动把落水收集成饮用水瓶，无电、无账单、无殖民者操作。</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -3780,6 +5065,257 @@
       <c r="C19" t="inlineStr">
         <is>
           <t>DLL + XML + 贴图 + 语言已部署 Steam 副本</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>⚠ 本表已过时：MEE_RainwaterCollector 已拆分为 MEE_SimpleRainwaterCollector 与 MEE_MoistureCollector，当前数据见『建筑』sheet。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>建筑（MEE 收集器，随 Metabolic Essential 模块开关显隐）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>即产即出：每攒够 1 份生水立即产出。spawnDefName=MEE_RawWater。数据取自当前 XML。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>DefName</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>中文名</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>成本(costList)</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>建造工时</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>血量</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>耗电(W)</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>日产(bottlesPerDay)</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>最大存量</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>产物</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>收集方式</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>需露天</t>
+        </is>
+      </c>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>设计分类</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>模块标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>MEE_MoistureCollector</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>水分收集器</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>WoodLogx50,Steelx25,ComponentIndustrialx1</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>MEE_RawWater</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>雨x2+空气x0.5+雪</t>
+        </is>
+      </c>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>MEEBuildingMarker</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>MEE_SimpleRainwaterCollector</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>简易雨水收集器</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>WoodLogx10</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>MEE_RawWater</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>雨x1</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>MEEBuildingMarker</t>
         </is>
       </c>
     </row>
